--- a/data/trans_orig/IP31KM01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM01_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>110313</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>103733</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114824</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91916</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86139</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96238</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>118652</t>
+          <t>90260</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>83966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127091</t>
+          <t>94580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>210569</t>
+          <t>200573</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192788</t>
+          <t>192479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>219422</t>
+          <t>207639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26317</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78753</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72309</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83610</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86310</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>80753</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>89463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>92,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>88316</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74378</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87071</t>
+          <t>91737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>168333</t>
+          <t>167069</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159707</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174632</t>
+          <t>173790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11127</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6270</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17571</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7082</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12639</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47869</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41675</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50872</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>48139</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44749</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49675</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53580</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>46269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57452</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101718</t>
+          <t>97883</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95678</t>
+          <t>91389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106048</t>
+          <t>102006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7975</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>183543</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>175110</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>189487</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>195302</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>185446</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>203071</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>198731</t>
+          <t>157034</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190174</t>
+          <t>148522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203947</t>
+          <t>163374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>394034</t>
+          <t>340577</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381639</t>
+          <t>329252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404582</t>
+          <t>349390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13770</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22203</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20235</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12466</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30091</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>129384</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119040</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>136010</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>102719</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>95677</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107298</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>142883</t>
+          <t>102197</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131181</t>
+          <t>95143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148803</t>
+          <t>107308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>245603</t>
+          <t>231581</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233921</t>
+          <t>219089</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254215</t>
+          <t>240530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41049</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>58197</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>52799</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>62048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>80,16%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>63460</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>58321</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>66325</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>64974</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54589</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64944</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>123172</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116388</t>
+          <t>115983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129499</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7666</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13064</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5435</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2570</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10574</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>608060</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>592319</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>621833</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>87,66%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>818</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>587846</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>574044</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>599398</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>656649</t>
+          <t>552796</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>635429</t>
+          <t>538478</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>672294</t>
+          <t>563499</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1244495</t>
+          <t>1160856</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1221402</t>
+          <t>1139476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1263304</t>
+          <t>1178173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>67635</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>53862</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>83376</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>57285</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>45733</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>71087</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75719</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60074</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96939</t>
+          <t>71754</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>133004</t>
+          <t>125071</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114195</t>
+          <t>107754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156097</t>
+          <t>146451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
